--- a/glossary.xlsx
+++ b/glossary.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26860" windowHeight="11640"/>
+    <workbookView windowWidth="28260" windowHeight="13960"/>
   </bookViews>
   <sheets>
     <sheet name="表格_20260416 (1)" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="243">
   <si>
     <r>
       <rPr>
@@ -1252,28 +1252,183 @@
     <t>keep shape after wash</t>
   </si>
   <si>
+    <t>前片</t>
+  </si>
+  <si>
     <t>FRONT</t>
   </si>
   <si>
-    <t>前片</t>
+    <t>后片</t>
   </si>
   <si>
     <t>BACK</t>
   </si>
   <si>
-    <t>后片</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>前中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>鸡心</t>
+    </r>
   </si>
   <si>
     <t>center front</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>前中</t>
+    <t>侧缝</t>
+  </si>
+  <si>
+    <t>side seam</t>
+  </si>
+  <si>
+    <t>无侧缝</t>
+  </si>
+  <si>
+    <t>no side seam</t>
+  </si>
+  <si>
+    <t>塞杯</t>
+  </si>
+  <si>
+    <t>removable cups inside</t>
+  </si>
+  <si>
+    <t>内侧有胸杯</t>
+  </si>
+  <si>
+    <t>padded cup inside</t>
+  </si>
+  <si>
+    <t>挤杯（有聚拢效果）</t>
+  </si>
+  <si>
+    <t>padded cup with push up inside</t>
+  </si>
+  <si>
+    <t>内侧有柔软胸杯</t>
+  </si>
+  <si>
+    <t>soft padded cup inside</t>
+  </si>
+  <si>
+    <t>有胸杯（必须薄且软）</t>
+  </si>
+  <si>
+    <t>padded cup (PADDING MUST BE THIN and SOFT)</t>
+  </si>
+  <si>
+    <t>push up</t>
+  </si>
+  <si>
+    <t>塞杯口</t>
+  </si>
+  <si>
+    <t>slit for removing the cup</t>
+  </si>
+  <si>
+    <t>内里有钢圈</t>
+  </si>
+  <si>
+    <t>wire inside</t>
+  </si>
+  <si>
+    <t>无钢圈</t>
+  </si>
+  <si>
+    <t>wireless</t>
+  </si>
+  <si>
+    <t>有胶骨</t>
+  </si>
+  <si>
+    <t>fishbone inside</t>
+  </si>
+  <si>
+    <t>宽弹性肩带</t>
+  </si>
+  <si>
+    <t>wide elastic straps</t>
+  </si>
+  <si>
+    <t>软弹性肩带</t>
+  </si>
+  <si>
+    <t>soft elastic strap</t>
+  </si>
+  <si>
+    <t>10mm哑光软弹性肩带</t>
+  </si>
+  <si>
+    <t>elastic shoulder strap, width = 10 mm, matte and soft</t>
+  </si>
+  <si>
+    <t>对折橡根有抓毛</t>
+  </si>
+  <si>
+    <t>folded elastic edge soft brushed</t>
+  </si>
+  <si>
+    <t>肩带从底端开始</t>
+  </si>
+  <si>
+    <t>strap from bottom up</t>
+  </si>
+  <si>
+    <t>打枣</t>
+  </si>
+  <si>
+    <t>bartacks / bartack</t>
+  </si>
+  <si>
+    <t>无缝</t>
+  </si>
+  <si>
+    <t>seamless</t>
+  </si>
+  <si>
+    <t>有金属丝的螺纹面料</t>
+  </si>
+  <si>
+    <t>elastic rib fabric with lurex</t>
+  </si>
+  <si>
+    <t>天鹅绒面料</t>
+  </si>
+  <si>
+    <t>velvet fabric</t>
+  </si>
+  <si>
+    <t>闪光面料</t>
+  </si>
+  <si>
+    <t>glitter fabric</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>定型纱</t>
     </r>
     <r>
       <rPr>
@@ -1289,156 +1444,179 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>鸡心</t>
-    </r>
-  </si>
-  <si>
-    <t>side seam</t>
-  </si>
-  <si>
-    <t>侧缝</t>
-  </si>
-  <si>
-    <t>no side seam</t>
-  </si>
-  <si>
-    <t>无侧缝</t>
-  </si>
-  <si>
-    <t>removable cups inside</t>
-  </si>
-  <si>
-    <t>塞杯</t>
-  </si>
-  <si>
-    <t>padded cup inside</t>
-  </si>
-  <si>
-    <t>内侧有胸杯</t>
-  </si>
-  <si>
-    <t>padded cup with push up inside</t>
-  </si>
-  <si>
-    <t>挤杯（有聚拢效果）</t>
-  </si>
-  <si>
-    <t>soft padded cup inside</t>
-  </si>
-  <si>
-    <t>内侧有柔软胸杯</t>
-  </si>
-  <si>
-    <t>padded cup (PADDING MUST BE THIN and SOFT)</t>
-  </si>
-  <si>
-    <t>有胸杯（必须薄且软）</t>
-  </si>
-  <si>
-    <t>push up</t>
-  </si>
-  <si>
-    <t>slit for removing the cup</t>
-  </si>
-  <si>
-    <t>塞杯口</t>
-  </si>
-  <si>
-    <t>wire inside</t>
-  </si>
-  <si>
-    <t>内里有钢圈</t>
-  </si>
-  <si>
-    <t>wireless</t>
-  </si>
-  <si>
-    <t>无钢圈</t>
-  </si>
-  <si>
-    <t>fishbone inside</t>
-  </si>
-  <si>
-    <t>有胶骨</t>
-  </si>
-  <si>
-    <t>wide elastic straps</t>
-  </si>
-  <si>
-    <t>宽弹性肩带</t>
-  </si>
-  <si>
-    <t>soft elastic strap</t>
-  </si>
-  <si>
-    <t>软弹性肩带</t>
-  </si>
-  <si>
-    <t>elastic shoulder strap, width = 10 mm, matte and soft</t>
-  </si>
-  <si>
-    <t>10mm哑光软弹性肩带</t>
-  </si>
-  <si>
-    <t>folded elastic edge soft brushed</t>
-  </si>
-  <si>
-    <t>对折橡根有抓毛</t>
-  </si>
-  <si>
-    <t>strap from bottom up</t>
-  </si>
-  <si>
-    <t>肩带从底端开始</t>
-  </si>
-  <si>
-    <t>bartacks / bartack</t>
-  </si>
-  <si>
-    <t>打枣</t>
-  </si>
-  <si>
-    <t>seamless</t>
-  </si>
-  <si>
-    <t>无缝</t>
-  </si>
-  <si>
-    <t>elastic rib fabric with lurex</t>
-  </si>
-  <si>
-    <t>有金属丝的螺纹面料</t>
-  </si>
-  <si>
-    <t>velvet fabric</t>
-  </si>
-  <si>
-    <t>天鹅绒面料</t>
-  </si>
-  <si>
-    <t>glitter fabric</t>
-  </si>
-  <si>
-    <t>闪光面料</t>
+      <t>网布</t>
+    </r>
   </si>
   <si>
     <t>strong mesh lining</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>定型纱</t>
-    </r>
+    <t>前片带弹性内衬</t>
+  </si>
+  <si>
+    <t>front part with elastic lining</t>
+  </si>
+  <si>
+    <t>前片双层面料</t>
+  </si>
+  <si>
+    <t>front part in double layer fabric</t>
+  </si>
+  <si>
+    <t>后片双层面料</t>
+  </si>
+  <si>
+    <t>back part in double layer fabric</t>
+  </si>
+  <si>
+    <t>双层面料</t>
+  </si>
+  <si>
+    <t>double layer(ed) fabric</t>
+  </si>
+  <si>
+    <t>下摆宽5.5cm</t>
+  </si>
+  <si>
+    <t>cuff 5,5 cm in width</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
+      <t>2.5cm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>支撑力强</t>
+    </r>
+  </si>
+  <si>
+    <t>2,5cm strong knitted</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1cm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>柔软橡根</t>
+    </r>
+  </si>
+  <si>
+    <t>1 cm soft elastic band</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1.2cm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>柔软橡根</t>
+    </r>
+  </si>
+  <si>
+    <t>1,2 cm soft elastic band</t>
+  </si>
+  <si>
+    <t>大钩编花边</t>
+  </si>
+  <si>
+    <t>big crochet border</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>自由裁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>热切</t>
+    </r>
+  </si>
+  <si>
+    <t>laser cut and glued edges</t>
+  </si>
+  <si>
+    <t>激光切边</t>
+  </si>
+  <si>
+    <t>edge laser cut</t>
+  </si>
+  <si>
+    <t>双针车线</t>
+  </si>
+  <si>
+    <t>2-needle stitching</t>
+  </si>
+  <si>
+    <t>人字车</t>
+  </si>
+  <si>
+    <t>zig-zag stitching</t>
+  </si>
+  <si>
+    <t>双人字车</t>
+  </si>
+  <si>
+    <t>double zig-zag stitching</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>内侧锁边</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>/</t>
     </r>
     <r>
@@ -1447,119 +1625,87 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>网布</t>
-    </r>
-  </si>
-  <si>
-    <t>front part with elastic lining</t>
-  </si>
-  <si>
-    <t>前片带弹性内衬</t>
-  </si>
-  <si>
-    <t>front part in double layer fabric</t>
-  </si>
-  <si>
-    <t>前片双层面料</t>
-  </si>
-  <si>
-    <t>back part in double layer fabric</t>
-  </si>
-  <si>
-    <t>后片双层面料</t>
-  </si>
-  <si>
-    <t>double layer(ed) fabric</t>
-  </si>
-  <si>
-    <t>双层面料</t>
-  </si>
-  <si>
-    <t>cuff 5,5 cm in width</t>
-  </si>
-  <si>
-    <t>下摆宽5.5cm</t>
-  </si>
-  <si>
-    <t>2,5cm strong knitted</t>
-  </si>
-  <si>
+      <t>打网线</t>
+    </r>
+  </si>
+  <si>
+    <t>inside flatlock stitching</t>
+  </si>
+  <si>
+    <t>后背勾扣</t>
+  </si>
+  <si>
+    <t>closure</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>后背勾扣：</t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
-      <t>2.5cm</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>支撑力强</t>
-    </r>
-  </si>
-  <si>
-    <t>1 cm soft elastic band</t>
-  </si>
-  <si>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>排</t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
-      <t>1cm</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>柔软橡根</t>
-    </r>
-  </si>
-  <si>
-    <t>1,2 cm soft elastic band</t>
-  </si>
-  <si>
+      <t>9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>扣，抓毛品质</t>
+    </r>
+  </si>
+  <si>
+    <t>closure: 3 hooks and 9 eyes, soft brushed</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>后背勾扣：</t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
-      <t>1.2cm</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>柔软橡根</t>
-    </r>
-  </si>
-  <si>
-    <t>big crochet border</t>
-  </si>
-  <si>
-    <t>大钩编花边</t>
-  </si>
-  <si>
-    <t>laser cut and glued edges</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>自由裁</t>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>排</t>
     </r>
     <r>
       <rPr>
@@ -1567,52 +1713,28 @@
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
-      <t>+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>热切</t>
-    </r>
-  </si>
-  <si>
-    <t>edge laser cut</t>
-  </si>
-  <si>
-    <t>激光切边</t>
-  </si>
-  <si>
-    <t>2-needle stitching</t>
-  </si>
-  <si>
-    <t>双针车线</t>
-  </si>
-  <si>
-    <t>zig-zag stitching</t>
-  </si>
-  <si>
-    <t>人字车</t>
-  </si>
-  <si>
-    <t>double zig-zag stitching</t>
-  </si>
-  <si>
-    <t>双人字车</t>
-  </si>
-  <si>
-    <t>inside flatlock stitching</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>内侧锁边</t>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>扣，抓毛品质</t>
+    </r>
+  </si>
+  <si>
+    <t>closure: 2 hooks &amp; 8 eyes, soft brushed</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>后背勾扣：</t>
     </r>
     <r>
       <rPr>
@@ -1620,34 +1742,15 @@
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>打网线</t>
-    </r>
-  </si>
-  <si>
-    <t>closure</t>
-  </si>
-  <si>
-    <t>后背勾扣</t>
-  </si>
-  <si>
-    <t>closure: 3 hooks and 9 eyes, soft brushed</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>后背勾扣：</t>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>排</t>
     </r>
     <r>
       <rPr>
@@ -1655,67 +1758,48 @@
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>排</t>
-    </r>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>扣，抓毛品质</t>
+    </r>
+  </si>
+  <si>
+    <t>closure: 2 hooks and 6 eyes, soft brushed</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
-      <t>9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>扣，抓毛品质</t>
-    </r>
-  </si>
-  <si>
-    <t>closure: 2 hooks &amp; 8 eyes, soft brushed</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>后背勾扣：</t>
-    </r>
+      <t>O</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>环</t>
+    </r>
+  </si>
+  <si>
+    <t>O-ring</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>排</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
       <t>8</t>
     </r>
     <r>
@@ -1724,72 +1808,6 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>扣，抓毛品质</t>
-    </r>
-  </si>
-  <si>
-    <t>closure: 2 hooks and 6 eyes, soft brushed</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>后背勾扣：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>排</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>扣，抓毛品质</t>
-    </r>
-  </si>
-  <si>
-    <t>O-ring</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>O</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
       <t>环</t>
     </r>
   </si>
@@ -1797,34 +1815,22 @@
     <t>8-ring</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>环</t>
-    </r>
+    <t>天鹅绒小花</t>
   </si>
   <si>
     <t>big velvet bow</t>
   </si>
   <si>
-    <t>天鹅绒小花</t>
+    <t>开口区域（无面料覆盖）</t>
   </si>
   <si>
     <t>area open, without fabric</t>
   </si>
   <si>
-    <t>开口区域（无面料覆盖）</t>
+    <t>氨纶</t>
+  </si>
+  <si>
+    <t>spandex</t>
   </si>
 </sst>
 </file>
@@ -1837,7 +1843,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1849,6 +1855,12 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体-简"/>
       <charset val="0"/>
     </font>
     <font>
@@ -2346,64 +2358,64 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2412,10 +2424,10 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2424,10 +2436,10 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2436,10 +2448,10 @@
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2448,10 +2460,10 @@
     <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2460,10 +2472,10 @@
     <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2472,11 +2484,11 @@
     <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2490,6 +2502,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3696,10 +3711,10 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B83" s="4" t="s">
         <v>164</v>
-      </c>
-      <c r="B83" s="4" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -4007,8 +4022,12 @@
       </c>
     </row>
     <row r="122" spans="1:2">
-      <c r="A122" s="4"/>
-      <c r="B122" s="4"/>
+      <c r="A122" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>242</v>
+      </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="4"/>

--- a/glossary.xlsx
+++ b/glossary.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="244">
   <si>
     <r>
       <rPr>
@@ -1831,6 +1831,9 @@
   </si>
   <si>
     <t>spandex</t>
+  </si>
+  <si>
+    <t>elastane</t>
   </si>
 </sst>
 </file>
@@ -4030,8 +4033,12 @@
       </c>
     </row>
     <row r="123" spans="1:2">
-      <c r="A123" s="4"/>
-      <c r="B123" s="4"/>
+      <c r="A123" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>243</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
